--- a/Översikt MÖNSTERÅS.xlsx
+++ b/Översikt MÖNSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45470</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45525</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44622</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>46148</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>45834</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>46196</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>44981</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>45086</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>45222</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>45904</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>44537</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>45679</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>44665</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>45222</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>46093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>44971</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>44627</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45406</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45054</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45152</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>46008</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>45160</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>45184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>46113</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>46206</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44791</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>45539</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>45282</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>45733</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45106</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>44621</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>45999</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>45674</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>46113</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45250</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>46138</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>45364</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>44873</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>44595</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>44993</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>45400</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>46283</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>44827</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>45455</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>44791</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>45540</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>45534</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45086</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>45350</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>45314</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>45456</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>45022</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>44966</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44967</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45525</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>45188</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>45091</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         <v>45405</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>46155</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>44939</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44875</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>45558</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>45534</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>45757</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>45833</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45453</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>44645</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45688</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>45792</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44634</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>44854</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>44827</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>44876</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45463</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>45086</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45278</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45538</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>45086</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>45174</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>46076</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>44827</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>45091</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>46206</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45434</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>46238</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44886</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45525</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>44511</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>44799</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>44753</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>44537</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>44604</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44487</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44824</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44651</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44690</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>44698</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44461</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44865</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>44865</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12338,7 +12338,7 @@
         <v>44459</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44546</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>44489</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>44606</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>44537</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>44649</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>44517</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44727</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>44882</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>44518</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>44519</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44573</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44475</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>44511</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>44820</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>44865</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44874</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>44621</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>44874</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>44644</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>44593</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>44642</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>44791</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>45250</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>45359</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>44537</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45114</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>44727</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>45057</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45161</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>45459</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45132</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>44879</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>44621</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45106</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>45028</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45569</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>45553</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>45540</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>45540</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>44802</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>45355</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>44923</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>44803</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45539</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45540</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>45209</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>44981</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>44874</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>45568</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45441</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>44511</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44922</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>44806</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>44928</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>45477</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>45162</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>44817</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>44974</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>45008</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45015</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45274</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45097</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>44813</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45364</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45097</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>44817</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>44638</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45274</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>45540</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>44917</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45091</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>44621</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>44865</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45764</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>46136</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45538</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>45769</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>46136</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>46136</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>46069</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>44593</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45903</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>46050</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45904</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45638</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>45686</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45538</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45152</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>46043</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>44972</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>44991</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45279</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>44904</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>44904</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45238</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45068</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45596</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45329</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45330</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45631</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45399</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>44600</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45274</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45961</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>44904</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45314</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45037</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45713</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45597</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>44981</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45272</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45034</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>45314</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45092</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45537</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45987</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45987</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>45987</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>46157</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45182</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>45988</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>45538</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45880</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>45404</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>45950</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>45015</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>44820</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45999</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>45999</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>44806</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45639</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45113</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45013</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>45764</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>44897</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>44979</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>45085</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>44802</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>46169</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>46169</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>45537</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45538</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>45271</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>45015</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>45086</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44931</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>45738</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45738</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>45169</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>45611</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45274</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>45022</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>46043</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45987</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>44915</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>46043</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>45686</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>44915</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>44915</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45139</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>46050</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>44817</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>44923</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>44869</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45575</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45685</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>44537</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45218</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45574</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>46078</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>45560</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>45160</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45400</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>46092</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>44904</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45280</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>46190</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>46094</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>46097</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>46160</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>46195</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>46171</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>46195</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>46149</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>46197</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>46196</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>45075</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>44950</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>45575</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>45188</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>46113</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>45089</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>45251</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>44869</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>46122</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45350</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>46244</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>46126</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>46202</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>44713</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>45155</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45182</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>46246</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>46204</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>45540</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>46134</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>45540</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>45188</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>44741</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27758,7 +27758,7 @@
         <v>45152</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45991</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>44593</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45321</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>44869</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>44922</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45251</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>46203</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>44923</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>44939</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45323</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>44739</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45218</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>46248</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>46205</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>46126</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45558</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>44872</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45645</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45106</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>44756</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>45764</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>45145</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>46255</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>44931</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45022</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44643</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45238</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>45054</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>45188</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45747</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44915</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>45715</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>46262</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45670</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>45091</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45560</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>46230</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>46275</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>46274</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>45649</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>45537</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30874,7 +30874,7 @@
         <v>45646</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>45714</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>45649</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>46238</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>45790</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45708</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45792</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>45792</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>46282</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>45701</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45805</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45805</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>45840</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45763</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45786</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45876</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>44614</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>45525</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>44981</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45468</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44942</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>44971</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>44545</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44677</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>44614</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>44690</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>44963</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45617</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45940</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>46003</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>46063</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>46097</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>

--- a/Översikt MÖNSTERÅS.xlsx
+++ b/Översikt MÖNSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45470</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45525</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44622</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>46148</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45834</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>46196</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>44981</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>45086</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45222</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>45904</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>44537</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>45679</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>44665</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45222</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>46093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44971</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>44627</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45406</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45152</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>46008</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>46113</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>45160</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>45184</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>46206</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>44791</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>45733</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45282</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>45250</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>45539</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>45674</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>46138</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>44621</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45106</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>45999</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45840</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>44873</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>44993</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>44595</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>46283</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>45364</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>45400</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>45490</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44827</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>45534</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>45086</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>45456</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>44791</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>45455</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>45350</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>45314</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>45540</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>46275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>45022</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>44966</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>44967</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>45525</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>44875</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>44939</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>45558</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>45833</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>46155</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45188</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>45405</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45091</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>45534</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>45757</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>44645</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45453</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>45688</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>45792</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>44634</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44827</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>44854</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>44876</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>46076</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>45174</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         <v>44886</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>45091</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>45434</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>45538</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>46206</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>46238</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>44827</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>45086</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45278</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>45463</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>45086</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>45525</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>44511</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>44799</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44753</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>44537</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44604</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>44824</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44487</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44651</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44690</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>44698</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44865</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44865</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>44546</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44489</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44537</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44606</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12549,7 +12549,7 @@
         <v>44649</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>44517</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>44727</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>44882</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12851,7 +12851,7 @@
         <v>44518</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44519</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>44475</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>44573</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>44511</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>44820</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44865</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44874</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44621</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44874</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>44644</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44593</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44642</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44791</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>44991</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45251</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44813</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45441</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>44817</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44974</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45271</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45459</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45279</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45708</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45013</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>44979</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45701</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45540</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>45540</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>45068</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>46043</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45987</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>44915</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>44915</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44915</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45091</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>46043</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45321</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45903</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>46050</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45904</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45569</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44874</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>44904</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>45008</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>45092</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>45805</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>46078</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>45560</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>44869</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>45145</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45152</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45805</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44915</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>45404</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>45037</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>44904</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>46092</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>44923</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>44923</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>46097</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>44638</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>45085</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>45597</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>44931</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17611,7 +17611,7 @@
         <v>45274</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>46113</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>44923</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>45015</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45251</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45961</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>46122</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45574</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45139</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>46126</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45161</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>46134</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>45553</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>45611</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45540</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>45764</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>46136</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>45274</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>44739</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45540</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45988</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45987</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>46136</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45987</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>45987</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>46136</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>45991</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>44922</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44593</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45686</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>45999</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>44869</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45738</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>45738</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>45769</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>45152</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>44806</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>46069</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45182</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45022</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>44817</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45188</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45160</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44621</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45713</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45538</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>46050</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44593</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>45054</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>46043</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45538</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45764</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>44972</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45950</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>45272</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>46157</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45880</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>45840</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>45686</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21938,7 +21938,7 @@
         <v>44950</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45250</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>45786</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         <v>45763</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>44537</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>44511</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>45538</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>45747</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45645</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>46169</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>46169</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>45114</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>45400</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45097</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>45764</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>45132</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>45162</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>44981</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>45106</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>45355</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>46190</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>45539</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>45540</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>46195</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>46195</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45089</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>46160</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45876</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>46196</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>46171</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>46197</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>45218</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>46202</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>45323</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>44643</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>45188</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>46203</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45638</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>46205</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>46204</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>46126</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45169</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>44806</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45685</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45097</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45209</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>44621</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>46255</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45155</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>45182</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45188</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>44802</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45314</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>44904</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>45314</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>45280</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>46262</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>45330</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>44600</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>44803</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>45015</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>46274</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>44939</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>46230</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45274</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>45537</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26806,7 +26806,7 @@
         <v>45075</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45113</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>45218</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>45274</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>46238</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>44802</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>46282</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>45022</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>46244</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44897</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>44879</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>44537</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>46288</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>44741</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>44869</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>45015</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>44817</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>44904</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>45999</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>46248</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28286,7 +28286,7 @@
         <v>45364</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>46246</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>45477</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28505,7 +28505,7 @@
         <v>44922</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>45575</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28651,7 +28651,7 @@
         <v>45568</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44713</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28802,7 +28802,7 @@
         <v>45639</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28875,7 +28875,7 @@
         <v>45238</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28948,7 +28948,7 @@
         <v>44917</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>44931</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29094,7 +29094,7 @@
         <v>44820</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>45057</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29240,7 +29240,7 @@
         <v>45537</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29313,7 +29313,7 @@
         <v>44865</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>45575</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29459,7 +29459,7 @@
         <v>45106</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>45034</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29610,7 +29610,7 @@
         <v>45596</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>44981</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>45329</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29829,7 +29829,7 @@
         <v>44727</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29902,7 +29902,7 @@
         <v>45359</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>45631</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>45238</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         <v>45028</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>45538</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30272,7 +30272,7 @@
         <v>45399</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>44928</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>45540</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>45350</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>44756</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30637,7 +30637,7 @@
         <v>45558</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30710,7 +30710,7 @@
         <v>44872</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45086</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30856,7 +30856,7 @@
         <v>45670</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45715</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45091</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45560</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>45649</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45714</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>45649</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31377,7 +31377,7 @@
         <v>45790</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31450,7 +31450,7 @@
         <v>45537</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>45646</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         <v>45792</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>45792</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>44614</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>44677</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>44614</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>44690</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>45525</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>44981</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>45468</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44942</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44971</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>44545</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>44963</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>45617</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45940</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>46003</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>46063</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>46097</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>

--- a/Översikt MÖNSTERÅS.xlsx
+++ b/Översikt MÖNSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45470</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45525</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44622</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>46148</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>45834</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>46196</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>44981</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>45086</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45222</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>45904</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>44537</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>45679</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>44665</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45222</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>46093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>44971</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>44627</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45406</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>46203</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>45054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>45152</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>46008</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>46113</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45160</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>45184</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>46206</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>44791</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45539</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>45282</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>45733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>45106</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>45674</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>45250</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45999</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>46138</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45840</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45364</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44873</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>44595</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>46283</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44993</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>45400</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>45490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44827</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>45455</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44791</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>45540</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>45534</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>45086</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>45350</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>46275</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45314</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>45456</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>45022</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>44966</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>44967</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         <v>45525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>45188</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45833</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45091</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>45405</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>46155</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>44939</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44875</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>45558</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>45534</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>45757</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>45453</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44645</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45688</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>45792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44854</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>44827</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>46076</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44886</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44876</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>45463</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>45086</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>45278</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>45538</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>45086</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>46206</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>45174</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>46238</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44827</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>45091</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>45434</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>45525</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44511</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44799</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>44753</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>44537</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44604</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>44487</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>44824</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44651</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>44690</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44698</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>44865</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44865</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44546</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44489</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44537</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>44606</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44649</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44517</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44727</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>44882</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44518</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44519</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>44573</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>44475</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>44511</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>44820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44874</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44865</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>44621</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>44874</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>44644</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>44593</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>44642</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>44791</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>45359</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         <v>45250</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14140,7 +14140,7 @@
         <v>44537</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>45114</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>44727</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>45459</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45161</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44879</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>45132</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>45057</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>44621</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>45106</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>45028</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45714</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44802</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>45649</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45569</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>45553</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>45540</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45540</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>45539</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>45540</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>45790</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>45355</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>44803</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>44923</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>45903</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>44874</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>45904</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>45209</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>46043</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>44981</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>45708</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16423,7 +16423,7 @@
         <v>45792</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45987</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45792</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>46043</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>45568</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>45701</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>46050</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>45805</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>45805</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>45441</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>44511</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>44922</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>44928</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>44806</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>45477</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>45162</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>46078</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>44817</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>44974</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         <v>45015</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45008</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45097</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45274</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>46092</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>44813</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>45961</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>45364</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>46097</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>45097</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>44817</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>44638</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>45274</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45987</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>46113</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45987</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45987</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>45988</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>46122</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>44917</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>46126</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45091</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>44865</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>46134</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45540</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45991</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>44593</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45840</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>44869</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>44922</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>45540</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45763</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>45786</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>44621</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45638</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45764</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>44972</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>45538</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44991</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45769</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45279</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44904</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>46136</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>44904</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>46136</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>46069</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>44593</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>46050</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21339,7 +21339,7 @@
         <v>45238</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>45686</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45538</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45152</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>46043</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>45068</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45596</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45329</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45330</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45631</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45399</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>44600</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45274</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>44904</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45314</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45037</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>46157</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45713</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45597</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44981</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45880</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>45272</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>45034</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45314</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45950</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45092</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45876</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>45537</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>46169</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45182</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45538</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45404</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45015</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44820</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>44806</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>45639</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>46190</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>45113</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>46160</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>45013</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>46195</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45764</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44897</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>46171</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>46195</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>44979</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>45085</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>46197</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>46196</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>44802</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45537</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45538</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>45271</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>45015</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>46202</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>45086</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>44931</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>46204</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45738</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>45738</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45169</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>45611</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>45274</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>46205</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>46126</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>45022</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>44915</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45686</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>44915</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>44915</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45139</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>44817</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44923</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>44869</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45575</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>45685</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>44537</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>45218</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>45574</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>46262</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45560</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>45160</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>46230</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>46274</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>46238</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>45400</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27637,7 +27637,7 @@
         <v>44904</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         <v>45280</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>46282</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>45075</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>44950</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>45575</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>46244</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45188</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>46288</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>46246</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>45089</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
         <v>45251</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>44869</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
         <v>45350</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>46248</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>46169</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>44713</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>45999</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45155</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>45182</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>45540</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>45188</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>44741</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>45152</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>45321</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>45251</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>44923</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>44939</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>46296</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29774,7 +29774,7 @@
         <v>45323</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>44739</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>45218</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>46255</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>46136</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>45558</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>44872</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>45645</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>45106</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>44756</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45764</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45145</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>44931</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30753,7 +30753,7 @@
         <v>45022</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>44643</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30899,7 +30899,7 @@
         <v>45238</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>45054</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>45188</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>45747</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>44915</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         <v>45715</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>45670</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>45091</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>45560</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45649</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>45537</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>45646</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44614</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>45525</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>44981</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45468</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>44942</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>44971</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>44545</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>44677</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>44614</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44690</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>44963</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>45617</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>45940</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>46003</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>46063</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>46097</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>

--- a/Översikt MÖNSTERÅS.xlsx
+++ b/Översikt MÖNSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45470</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45525</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44622</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>46148</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1604,24 +1604,24 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S 1703-2024</t>
+          <t>A 42153-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45434</v>
+        <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1634,19 +1634,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>30.3</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
         <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1658,21 +1658,144 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
       </c>
       <c r="T9" t="n">
+        <v>45</v>
+      </c>
+      <c r="U9" t="n">
+        <v>45</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Kolflarnlav
+Rynkskinn
+Tallticka
+Talltita
+Ullticka
+Vedskivlav
+Blodticka
+Blåmossa
+Brandticka
+Grovticka
+Vågbandad barkbock
+Spillkråka
+Tjäder
+Tofsmes
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/A 42153-2025 artfynd.xlsx", "A 42153-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/A 42153-2025 karta.png", "A 42153-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/A 42153-2025 georefererad karta.tif", "A 42153-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/A 42153-2025 FSC-klagomål.docx", "A 42153-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/A 42153-2025 FSC-klagomål mail.docx", "A 42153-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/A 42153-2025 tillsynsbegäran.docx", "A 42153-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/A 42153-2025 tillsynsbegäran mail.docx", "A 42153-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/fåglar/A 42153-2025 prioriterade fågelarter.docx", "A 42153-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S 1703-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="n">
         <v>39</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>13</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Sydpipistrell
@@ -1691,111 +1814,111 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/S 1703-2024 artfynd.xlsx", "S 1703-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/S 1703-2024 karta.png", "S 1703-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/S 1703-2024 georefererad karta.tif", "S 1703-2024")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/knärot/S 1703-2024 karta knärot.png", "S 1703-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/S 1703-2024 FSC-klagomål.docx", "S 1703-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/S 1703-2024 FSC-klagomål mail.docx", "S 1703-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/S 1703-2024 tillsynsbegäran.docx", "S 1703-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/S 1703-2024 tillsynsbegäran mail.docx", "S 1703-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 31889-2025</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D11" s="1" t="n">
         <v>45834</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>4.3</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>11</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" t="n">
         <v>3</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>14</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>21</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>19</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Talltita
@@ -1813,111 +1936,111 @@
 Ärtsångare</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/A 31889-2025 artfynd.xlsx", "A 31889-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/A 31889-2025 karta.png", "A 31889-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/A 31889-2025 georefererad karta.tif", "A 31889-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/A 31889-2025 FSC-klagomål.docx", "A 31889-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/A 31889-2025 FSC-klagomål mail.docx", "A 31889-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/A 31889-2025 tillsynsbegäran.docx", "A 31889-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/A 31889-2025 tillsynsbegäran mail.docx", "A 31889-2025")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/fåglar/A 31889-2025 prioriterade fågelarter.docx", "A 31889-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>S 1795-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>46196</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>18.8</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" t="n">
         <v>4</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>9</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>10</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S12" t="n">
         <v>14</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>36</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Läderbagge
 Ekticka
@@ -1935,107 +2058,107 @@
 Jättesvampmal</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/S 1795-2026 artfynd.xlsx", "S 1795-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/S 1795-2026 karta.png", "S 1795-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/S 1795-2026 georefererad karta.tif", "S 1795-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/S 1795-2026 FSC-klagomål.docx", "S 1795-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/S 1795-2026 FSC-klagomål mail.docx", "S 1795-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/S 1795-2026 tillsynsbegäran.docx", "S 1795-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/S 1795-2026 tillsynsbegäran mail.docx", "S 1795-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>S 758-2023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>44981</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>25.8</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>10</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>7</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>7</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>13</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" t="n">
         <v>46</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U13" t="n">
         <v>1</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Barbastell
 Grönsångare
@@ -2052,111 +2175,111 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/S 758-2023 artfynd.xlsx", "S 758-2023")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/S 758-2023 karta.png", "S 758-2023")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/S 758-2023 georefererad karta.tif", "S 758-2023")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/S 758-2023 FSC-klagomål.docx", "S 758-2023")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/S 758-2023 FSC-klagomål mail.docx", "S 758-2023")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/S 758-2023 tillsynsbegäran.docx", "S 758-2023")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/S 758-2023 tillsynsbegäran mail.docx", "S 758-2023")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/fåglar/S 758-2023 prioriterade fågelarter.docx", "S 758-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 25231-2023</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>45086</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>6.4</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>12</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>6</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>12</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>17</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>5</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Barbastell
 Brunlångöra
@@ -2172,116 +2295,116 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/A 25231-2023 artfynd.xlsx", "A 25231-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/A 25231-2023 karta.png", "A 25231-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/A 25231-2023 georefererad karta.tif", "A 25231-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/A 25231-2023 FSC-klagomål.docx", "A 25231-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/A 25231-2023 FSC-klagomål mail.docx", "A 25231-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/A 25231-2023 tillsynsbegäran.docx", "A 25231-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/A 25231-2023 tillsynsbegäran mail.docx", "A 25231-2023")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/fåglar/A 25231-2023 prioriterade fågelarter.docx", "A 25231-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>S 3727-2023</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>45222</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="E15" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>25.6</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>4</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>7</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>1</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>8</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R15" t="n">
         <v>1</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S15" t="n">
         <v>12</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>42</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Ask
 Ekticka
@@ -2297,175 +2420,56 @@
 Sotlav</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/S 3727-2023 artfynd.xlsx", "S 3727-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/S 3727-2023 karta.png", "S 3727-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/S 3727-2023 georefererad karta.tif", "S 3727-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/S 3727-2023 FSC-klagomål.docx", "S 3727-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/S 3727-2023 FSC-klagomål mail.docx", "S 3727-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/S 3727-2023 tillsynsbegäran.docx", "S 3727-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/S 3727-2023 tillsynsbegäran mail.docx", "S 3727-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 42153-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45904</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>11</v>
-      </c>
-      <c r="T15" t="n">
-        <v>38</v>
-      </c>
-      <c r="U15" t="n">
-        <v>38</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Kolflarnlav
-Rynkskinn
-Tallticka
-Talltita
-Ullticka
-Vedskivlav
-Blåmossa
-Brandticka
-Vågbandad barkbock
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/A 42153-2025 artfynd.xlsx", "A 42153-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/A 42153-2025 karta.png", "A 42153-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/A 42153-2025 georefererad karta.tif", "A 42153-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/A 42153-2025 FSC-klagomål.docx", "A 42153-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/A 42153-2025 FSC-klagomål mail.docx", "A 42153-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/A 42153-2025 tillsynsbegäran.docx", "A 42153-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/A 42153-2025 tillsynsbegäran mail.docx", "A 42153-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/fåglar/A 42153-2025 prioriterade fågelarter.docx", "A 42153-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S 10038-2021</t>
+          <t>A 29379-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44537</v>
+        <v>46203</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2477,26 +2481,21 @@
           <t>MÖNSTERÅS</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="L16" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2507,21 +2506,149 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>11</v>
       </c>
       <c r="T16" t="n">
+        <v>36</v>
+      </c>
+      <c r="U16" t="n">
+        <v>36</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knärot
+Gropticka
+Motaggsvamp
+Tallticka
+Blomkålssvamp
+Blåmossa
+Grönpyrola
+Spillkråka
+Tofsmes
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/A 29379-2026 artfynd.xlsx", "A 29379-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/A 29379-2026 karta.png", "A 29379-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/A 29379-2026 georefererad karta.tif", "A 29379-2026")</f>
+        <v/>
+      </c>
+      <c r="Z16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/knärot/A 29379-2026 karta knärot.png", "A 29379-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/A 29379-2026 FSC-klagomål.docx", "A 29379-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/A 29379-2026 FSC-klagomål mail.docx", "A 29379-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/A 29379-2026 tillsynsbegäran.docx", "A 29379-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/A 29379-2026 tillsynsbegäran mail.docx", "A 29379-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0861/fåglar/A 29379-2026 prioriterade fågelarter.docx", "A 29379-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S 10038-2021</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Åtgärd i nyckelbiotop</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44537</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
         <v>12</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Glänsande blombagge
 Hjärtstilla
@@ -2536,111 +2663,111 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/S 10038-2021 artfynd.xlsx", "S 10038-2021")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/S 10038-2021 karta.png", "S 10038-2021")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/S 10038-2021 georefererad karta.tif", "S 10038-2021")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/S 10038-2021 FSC-klagomål.docx", "S 10038-2021")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/S 10038-2021 FSC-klagomål mail.docx", "S 10038-2021")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/S 10038-2021 tillsynsbegäran.docx", "S 10038-2021")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/S 10038-2021 tillsynsbegäran mail.docx", "S 10038-2021")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/fåglar/S 10038-2021 prioriterade fågelarter.docx", "S 10038-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 3290-2025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45679</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>3.5</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>7</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>3</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>4</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>10</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>65</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>49</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Duvhök
@@ -2654,115 +2781,115 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/A 3290-2025 artfynd.xlsx", "A 3290-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/A 3290-2025 karta.png", "A 3290-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/A 3290-2025 georefererad karta.tif", "A 3290-2025")</f>
         <v/>
       </c>
-      <c r="Z17">
+      <c r="Z18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/knärot/A 3290-2025 karta knärot.png", "A 3290-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/A 3290-2025 FSC-klagomål.docx", "A 3290-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/A 3290-2025 FSC-klagomål mail.docx", "A 3290-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/A 3290-2025 tillsynsbegäran.docx", "A 3290-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/A 3290-2025 tillsynsbegäran mail.docx", "A 3290-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/fåglar/A 3290-2025 prioriterade fågelarter.docx", "A 3290-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 34337-2025</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45846</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>4.5</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>7</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L19" t="n">
         <v>4</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>4</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>10</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>23</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>21</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Tallticka
@@ -2776,111 +2903,111 @@
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/A 34337-2025 artfynd.xlsx", "A 34337-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/A 34337-2025 karta.png", "A 34337-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/A 34337-2025 georefererad karta.tif", "A 34337-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/A 34337-2025 FSC-klagomål.docx", "A 34337-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/A 34337-2025 FSC-klagomål mail.docx", "A 34337-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/A 34337-2025 tillsynsbegäran.docx", "A 34337-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/A 34337-2025 tillsynsbegäran mail.docx", "A 34337-2025")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/fåglar/A 34337-2025 prioriterade fågelarter.docx", "A 34337-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>S 2019-2022</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>44665</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>10.4</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>10</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>3</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>10</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>28</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>1</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Barbastell
 Brunlångöra
@@ -2894,112 +3021,112 @@
 Skogsödla</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/S 2019-2022 artfynd.xlsx", "S 2019-2022")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/S 2019-2022 karta.png", "S 2019-2022")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/S 2019-2022 georefererad karta.tif", "S 2019-2022")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/S 2019-2022 FSC-klagomål.docx", "S 2019-2022")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/S 2019-2022 FSC-klagomål mail.docx", "S 2019-2022")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/S 2019-2022 tillsynsbegäran.docx", "S 2019-2022")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/S 2019-2022 tillsynsbegäran mail.docx", "S 2019-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>S 3730-2023</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>45222</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>5.3</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>6</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>7</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>10</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>27</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Läderbagge
 Gammelekslav
@@ -3013,107 +3140,107 @@
 Utter</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/S 3730-2023 artfynd.xlsx", "S 3730-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/S 3730-2023 karta.png", "S 3730-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/S 3730-2023 georefererad karta.tif", "S 3730-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/S 3730-2023 FSC-klagomål.docx", "S 3730-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/S 3730-2023 FSC-klagomål mail.docx", "S 3730-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/S 3730-2023 tillsynsbegäran.docx", "S 3730-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/S 3730-2023 tillsynsbegäran mail.docx", "S 3730-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>S 720-2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>46093</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>35.9</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>4</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>3</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>10</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>16</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Nordfladdermus
@@ -3127,111 +3254,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/S 720-2026 artfynd.xlsx", "S 720-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/S 720-2026 karta.png", "S 720-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/S 720-2026 georefererad karta.tif", "S 720-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/S 720-2026 FSC-klagomål.docx", "S 720-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/S 720-2026 FSC-klagomål mail.docx", "S 720-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/S 720-2026 tillsynsbegäran.docx", "S 720-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/S 720-2026 tillsynsbegäran mail.docx", "S 720-2026")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/fåglar/S 720-2026 prioriterade fågelarter.docx", "S 720-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 7475-2023</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D23" s="1" t="n">
         <v>44971</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>3.3</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>3</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>3</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>4</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>5</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>1</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>9</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>44</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>44</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Grönsångare
@@ -3244,115 +3371,115 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/A 7475-2023 artfynd.xlsx", "A 7475-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/A 7475-2023 karta.png", "A 7475-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/A 7475-2023 georefererad karta.tif", "A 7475-2023")</f>
         <v/>
       </c>
-      <c r="Z22">
+      <c r="Z23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/knärot/A 7475-2023 karta knärot.png", "A 7475-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/A 7475-2023 FSC-klagomål.docx", "A 7475-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/A 7475-2023 FSC-klagomål mail.docx", "A 7475-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/A 7475-2023 tillsynsbegäran.docx", "A 7475-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/A 7475-2023 tillsynsbegäran mail.docx", "A 7475-2023")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/fåglar/A 7475-2023 prioriterade fågelarter.docx", "A 7475-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>S 1302-2022</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>44627</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>3.2</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>5</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>4</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>9</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>16</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Blåmossa
@@ -3365,107 +3492,107 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/S 1302-2022 artfynd.xlsx", "S 1302-2022")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/S 1302-2022 karta.png", "S 1302-2022")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/S 1302-2022 georefererad karta.tif", "S 1302-2022")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/S 1302-2022 FSC-klagomål.docx", "S 1302-2022")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/S 1302-2022 FSC-klagomål mail.docx", "S 1302-2022")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/S 1302-2022 tillsynsbegäran.docx", "S 1302-2022")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/S 1302-2022 tillsynsbegäran mail.docx", "S 1302-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>S 1326-2024</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>45406</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>3.2</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>5</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K25" t="n">
         <v>4</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>9</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>16</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Kattfotslav
 Blåmossa
@@ -3478,148 +3605,32 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/S 1326-2024 artfynd.xlsx", "S 1326-2024")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/S 1326-2024 karta.png", "S 1326-2024")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/S 1326-2024 georefererad karta.tif", "S 1326-2024")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/S 1326-2024 FSC-klagomål.docx", "S 1326-2024")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/S 1326-2024 FSC-klagomål mail.docx", "S 1326-2024")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/S 1326-2024 tillsynsbegäran.docx", "S 1326-2024")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/S 1326-2024 tillsynsbegäran mail.docx", "S 1326-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 29379-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2</v>
-      </c>
-      <c r="S25" t="n">
-        <v>8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>27</v>
-      </c>
-      <c r="U25" t="n">
-        <v>27</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Knärot
-Motaggsvamp
-Tallticka
-Blomkålssvamp
-Blåmossa
-Grönpyrola
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/artfynd/A 29379-2026 artfynd.xlsx", "A 29379-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor/A 29379-2026 karta.png", "A 29379-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/kartor_geotiff/A 29379-2026 georefererad karta.tif", "A 29379-2026")</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/knärot/A 29379-2026 karta knärot.png", "A 29379-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomål/A 29379-2026 FSC-klagomål.docx", "A 29379-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/klagomålsmail/A 29379-2026 FSC-klagomål mail.docx", "A 29379-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsyn/A 29379-2026 tillsynsbegäran.docx", "A 29379-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0861/tillsynsmail/A 29379-2026 tillsynsbegäran mail.docx", "A 29379-2026")</f>
         <v/>
       </c>
     </row>
@@ -3643,7 +3654,7 @@
         <v>45054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3760,7 +3771,7 @@
         <v>45152</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3885,7 +3896,7 @@
         <v>46008</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3997,7 +4008,7 @@
         <v>46113</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4117,7 +4128,7 @@
         <v>45160</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4232,7 +4243,7 @@
         <v>45184</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4347,7 +4358,7 @@
         <v>46206</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4467,7 +4478,7 @@
         <v>44791</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4585,7 +4596,7 @@
         <v>45539</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4694,7 +4705,7 @@
         <v>45282</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4811,7 +4822,7 @@
         <v>45733</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4928,7 +4939,7 @@
         <v>45106</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5041,7 +5052,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5154,7 +5165,7 @@
         <v>45674</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5263,7 +5274,7 @@
         <v>45250</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5380,7 +5391,7 @@
         <v>45999</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5498,7 +5509,7 @@
         <v>46138</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5611,7 +5622,7 @@
         <v>45840</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5723,7 +5734,7 @@
         <v>45364</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5840,7 +5851,7 @@
         <v>44873</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5957,7 +5968,7 @@
         <v>44595</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6065,7 +6076,7 @@
         <v>46283</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6177,7 +6188,7 @@
         <v>44993</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6289,7 +6300,7 @@
         <v>45400</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6405,7 +6416,7 @@
         <v>45490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6513,7 +6524,7 @@
         <v>44827</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6620,7 +6631,7 @@
         <v>45455</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6727,7 +6738,7 @@
         <v>44791</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6838,7 +6849,7 @@
         <v>45540</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6945,7 +6956,7 @@
         <v>45534</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7056,7 +7067,7 @@
         <v>45086</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7163,7 +7174,7 @@
         <v>45350</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7279,7 +7290,7 @@
         <v>46275</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7330,10 +7341,10 @@
         <v>3</v>
       </c>
       <c r="T58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
@@ -7391,7 +7402,7 @@
         <v>45314</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7498,7 +7509,7 @@
         <v>45456</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7605,7 +7616,7 @@
         <v>45022</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7712,7 +7723,7 @@
         <v>44966</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7823,7 +7834,7 @@
         <v>44967</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7930,7 +7941,7 @@
         <v>45525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8037,7 +8048,7 @@
         <v>45188</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8143,7 +8154,7 @@
         <v>45833</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8253,7 +8264,7 @@
         <v>45091</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8359,7 +8370,7 @@
         <v>45405</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8473,7 +8484,7 @@
         <v>46155</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8584,7 +8595,7 @@
         <v>44939</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8690,7 +8701,7 @@
         <v>44875</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8796,7 +8807,7 @@
         <v>45558</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8902,7 +8913,7 @@
         <v>45534</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9017,7 +9028,7 @@
         <v>45757</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9132,7 +9143,7 @@
         <v>45453</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9242,7 +9253,7 @@
         <v>44645</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9348,7 +9359,7 @@
         <v>45688</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9458,7 +9469,7 @@
         <v>45792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9568,7 +9579,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9677,7 +9688,7 @@
         <v>44854</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9786,7 +9797,7 @@
         <v>44827</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9896,7 +9907,7 @@
         <v>46076</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10001,7 +10012,7 @@
         <v>44886</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10110,7 +10121,7 @@
         <v>44876</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10219,7 +10230,7 @@
         <v>45463</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10324,7 +10335,7 @@
         <v>45086</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10429,7 +10440,7 @@
         <v>45278</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10534,7 +10545,7 @@
         <v>45538</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10639,7 +10650,7 @@
         <v>45086</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10744,7 +10755,7 @@
         <v>46206</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10854,7 +10865,7 @@
         <v>45174</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10959,7 +10970,7 @@
         <v>46238</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11064,7 +11075,7 @@
         <v>44827</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11169,7 +11180,7 @@
         <v>45091</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11278,7 +11289,7 @@
         <v>45434</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11392,7 +11403,7 @@
         <v>45525</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11497,7 +11508,7 @@
         <v>44511</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11570,7 +11581,7 @@
         <v>44799</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11643,7 +11654,7 @@
         <v>44753</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11716,7 +11727,7 @@
         <v>44537</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11789,7 +11800,7 @@
         <v>44604</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11862,7 +11873,7 @@
         <v>44487</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11935,7 +11946,7 @@
         <v>44824</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12008,7 +12019,7 @@
         <v>44651</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12081,7 +12092,7 @@
         <v>44690</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12154,7 +12165,7 @@
         <v>44698</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12227,7 +12238,7 @@
         <v>44865</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12300,7 +12311,7 @@
         <v>44865</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12373,7 +12384,7 @@
         <v>44546</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12446,7 +12457,7 @@
         <v>44489</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12519,7 +12530,7 @@
         <v>44537</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12592,7 +12603,7 @@
         <v>44606</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12665,7 +12676,7 @@
         <v>44649</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12743,7 +12754,7 @@
         <v>44517</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12821,7 +12832,7 @@
         <v>44727</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12894,7 +12905,7 @@
         <v>44882</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12967,7 +12978,7 @@
         <v>44518</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13040,7 +13051,7 @@
         <v>44519</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13113,7 +13124,7 @@
         <v>44573</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13186,7 +13197,7 @@
         <v>44475</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13259,7 +13270,7 @@
         <v>44511</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13332,7 +13343,7 @@
         <v>44820</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13405,7 +13416,7 @@
         <v>44874</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13478,7 +13489,7 @@
         <v>44865</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13551,7 +13562,7 @@
         <v>44621</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13624,7 +13635,7 @@
         <v>44874</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13697,7 +13708,7 @@
         <v>44644</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13770,7 +13781,7 @@
         <v>44593</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13843,7 +13854,7 @@
         <v>44642</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13921,7 +13932,7 @@
         <v>44791</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13994,7 +14005,7 @@
         <v>45359</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14067,7 +14078,7 @@
         <v>45250</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14140,7 +14151,7 @@
         <v>44537</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14213,7 +14224,7 @@
         <v>45114</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14291,7 +14302,7 @@
         <v>44727</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14364,7 +14375,7 @@
         <v>45459</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14437,7 +14448,7 @@
         <v>45161</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14510,7 +14521,7 @@
         <v>44879</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14583,7 +14594,7 @@
         <v>45132</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14656,7 +14667,7 @@
         <v>45057</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14729,7 +14740,7 @@
         <v>44621</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14802,7 +14813,7 @@
         <v>45106</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14880,7 +14891,7 @@
         <v>45028</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14953,7 +14964,7 @@
         <v>45714</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15026,7 +15037,7 @@
         <v>44802</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15099,7 +15110,7 @@
         <v>45649</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15177,7 +15188,7 @@
         <v>45569</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15250,7 +15261,7 @@
         <v>45553</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15323,7 +15334,7 @@
         <v>45540</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15396,7 +15407,7 @@
         <v>45540</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15469,7 +15480,7 @@
         <v>45539</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15542,7 +15553,7 @@
         <v>45540</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15615,7 +15626,7 @@
         <v>45790</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15688,7 +15699,7 @@
         <v>45355</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15761,7 +15772,7 @@
         <v>44803</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15839,7 +15850,7 @@
         <v>44923</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15912,7 +15923,7 @@
         <v>45903</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15985,7 +15996,7 @@
         <v>44874</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16058,7 +16069,7 @@
         <v>45904</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16131,7 +16142,7 @@
         <v>45209</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16204,7 +16215,7 @@
         <v>46043</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16277,7 +16288,7 @@
         <v>44981</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16350,7 +16361,7 @@
         <v>45708</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16423,7 +16434,7 @@
         <v>45792</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16496,7 +16507,7 @@
         <v>45987</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16569,7 +16580,7 @@
         <v>45792</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16642,7 +16653,7 @@
         <v>46043</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16715,7 +16726,7 @@
         <v>45568</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16793,7 +16804,7 @@
         <v>45701</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16866,7 +16877,7 @@
         <v>46050</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16939,7 +16950,7 @@
         <v>45805</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17012,7 +17023,7 @@
         <v>45805</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17085,7 +17096,7 @@
         <v>45441</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17158,7 +17169,7 @@
         <v>44511</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17231,7 +17242,7 @@
         <v>44922</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17304,7 +17315,7 @@
         <v>44928</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17377,7 +17388,7 @@
         <v>44806</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17450,7 +17461,7 @@
         <v>45477</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17523,7 +17534,7 @@
         <v>45162</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17596,7 +17607,7 @@
         <v>46078</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17669,7 +17680,7 @@
         <v>44817</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17742,7 +17753,7 @@
         <v>44974</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17820,7 +17831,7 @@
         <v>45015</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17893,7 +17904,7 @@
         <v>45008</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17966,7 +17977,7 @@
         <v>45097</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18039,7 +18050,7 @@
         <v>45274</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18112,7 +18123,7 @@
         <v>46092</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18185,7 +18196,7 @@
         <v>44813</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18258,7 +18269,7 @@
         <v>45961</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18331,7 +18342,7 @@
         <v>45364</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18404,7 +18415,7 @@
         <v>46097</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18477,7 +18488,7 @@
         <v>45097</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18550,7 +18561,7 @@
         <v>44817</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18628,7 +18639,7 @@
         <v>44638</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18701,7 +18712,7 @@
         <v>45274</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18774,7 +18785,7 @@
         <v>45987</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18847,7 +18858,7 @@
         <v>46113</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18925,7 +18936,7 @@
         <v>45987</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18998,7 +19009,7 @@
         <v>45987</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19071,7 +19082,7 @@
         <v>45988</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19144,7 +19155,7 @@
         <v>46122</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19217,7 +19228,7 @@
         <v>44917</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19290,7 +19301,7 @@
         <v>46126</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19363,7 +19374,7 @@
         <v>45091</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19436,7 +19447,7 @@
         <v>44865</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19509,7 +19520,7 @@
         <v>46134</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19582,7 +19593,7 @@
         <v>45540</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19655,7 +19666,7 @@
         <v>45991</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19733,7 +19744,7 @@
         <v>44593</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19806,7 +19817,7 @@
         <v>45840</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19879,7 +19890,7 @@
         <v>44869</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19952,7 +19963,7 @@
         <v>44922</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20025,7 +20036,7 @@
         <v>45540</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20098,7 +20109,7 @@
         <v>45763</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20171,7 +20182,7 @@
         <v>45786</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20244,7 +20255,7 @@
         <v>44621</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20317,7 +20328,7 @@
         <v>45638</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20390,7 +20401,7 @@
         <v>45764</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20463,7 +20474,7 @@
         <v>44972</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20536,7 +20547,7 @@
         <v>45538</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20609,7 +20620,7 @@
         <v>44991</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20682,7 +20693,7 @@
         <v>45769</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20755,7 +20766,7 @@
         <v>45279</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20828,7 +20839,7 @@
         <v>44904</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20901,7 +20912,7 @@
         <v>46136</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20974,7 +20985,7 @@
         <v>44904</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21047,7 +21058,7 @@
         <v>46136</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21120,7 +21131,7 @@
         <v>46069</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21193,7 +21204,7 @@
         <v>44593</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21266,7 +21277,7 @@
         <v>46050</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21339,7 +21350,7 @@
         <v>45238</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21412,7 +21423,7 @@
         <v>45686</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21485,7 +21496,7 @@
         <v>45538</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21558,7 +21569,7 @@
         <v>45152</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21636,7 +21647,7 @@
         <v>46043</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21709,7 +21720,7 @@
         <v>45068</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21782,7 +21793,7 @@
         <v>45596</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21855,7 +21866,7 @@
         <v>45329</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21928,7 +21939,7 @@
         <v>45330</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22001,7 +22012,7 @@
         <v>45631</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22079,7 +22090,7 @@
         <v>45399</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22152,7 +22163,7 @@
         <v>44600</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22225,7 +22236,7 @@
         <v>45274</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22298,7 +22309,7 @@
         <v>44904</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22371,7 +22382,7 @@
         <v>45314</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22444,7 +22455,7 @@
         <v>45037</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22517,7 +22528,7 @@
         <v>46157</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22590,7 +22601,7 @@
         <v>45713</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22663,7 +22674,7 @@
         <v>45597</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22736,7 +22747,7 @@
         <v>44981</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22809,7 +22820,7 @@
         <v>45880</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22882,7 +22893,7 @@
         <v>45272</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22955,7 +22966,7 @@
         <v>45034</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23028,7 +23039,7 @@
         <v>45314</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23101,7 +23112,7 @@
         <v>45950</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23174,7 +23185,7 @@
         <v>45092</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23247,7 +23258,7 @@
         <v>45876</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23320,7 +23331,7 @@
         <v>45537</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23393,7 +23404,7 @@
         <v>46169</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23466,7 +23477,7 @@
         <v>45182</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23539,7 +23550,7 @@
         <v>45538</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23612,7 +23623,7 @@
         <v>45404</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23685,7 +23696,7 @@
         <v>45015</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23758,7 +23769,7 @@
         <v>44820</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23831,7 +23842,7 @@
         <v>44806</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23904,7 +23915,7 @@
         <v>45639</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23977,7 +23988,7 @@
         <v>46190</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24050,7 +24061,7 @@
         <v>45113</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24123,7 +24134,7 @@
         <v>46160</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24201,7 +24212,7 @@
         <v>45013</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24274,7 +24285,7 @@
         <v>46195</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24347,7 +24358,7 @@
         <v>45764</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24420,7 +24431,7 @@
         <v>44897</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24498,7 +24509,7 @@
         <v>46171</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24571,7 +24582,7 @@
         <v>46195</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24644,7 +24655,7 @@
         <v>44979</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24717,7 +24728,7 @@
         <v>45085</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24790,7 +24801,7 @@
         <v>46197</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24863,7 +24874,7 @@
         <v>46196</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24936,7 +24947,7 @@
         <v>44802</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25009,7 +25020,7 @@
         <v>45537</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25082,7 +25093,7 @@
         <v>45538</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25155,7 +25166,7 @@
         <v>45271</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25228,7 +25239,7 @@
         <v>45015</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25301,7 +25312,7 @@
         <v>46202</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25374,7 +25385,7 @@
         <v>45086</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25447,7 +25458,7 @@
         <v>44931</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25520,7 +25531,7 @@
         <v>46204</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25593,7 +25604,7 @@
         <v>45738</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25666,7 +25677,7 @@
         <v>45738</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25739,7 +25750,7 @@
         <v>45169</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25812,7 +25823,7 @@
         <v>45611</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25885,7 +25896,7 @@
         <v>45274</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25958,7 +25969,7 @@
         <v>46205</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26031,7 +26042,7 @@
         <v>46126</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26104,7 +26115,7 @@
         <v>45022</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26177,7 +26188,7 @@
         <v>44915</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26250,7 +26261,7 @@
         <v>45686</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26323,7 +26334,7 @@
         <v>44915</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26396,7 +26407,7 @@
         <v>44915</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26469,7 +26480,7 @@
         <v>45139</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26542,7 +26553,7 @@
         <v>44817</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26615,7 +26626,7 @@
         <v>44923</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26688,7 +26699,7 @@
         <v>44869</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26761,7 +26772,7 @@
         <v>45575</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26834,7 +26845,7 @@
         <v>45685</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26907,7 +26918,7 @@
         <v>44537</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26980,7 +26991,7 @@
         <v>45218</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27053,7 +27064,7 @@
         <v>45574</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27126,7 +27137,7 @@
         <v>46262</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27199,7 +27210,7 @@
         <v>45560</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27272,7 +27283,7 @@
         <v>45160</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27345,7 +27356,7 @@
         <v>46230</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27418,7 +27429,7 @@
         <v>46274</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27491,7 +27502,7 @@
         <v>46238</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27564,7 +27575,7 @@
         <v>45400</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27637,7 +27648,7 @@
         <v>44904</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27710,7 +27721,7 @@
         <v>45280</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27788,7 +27799,7 @@
         <v>46282</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27861,7 +27872,7 @@
         <v>45075</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27934,7 +27945,7 @@
         <v>44950</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28007,7 +28018,7 @@
         <v>45575</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28080,7 +28091,7 @@
         <v>46244</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28158,7 +28169,7 @@
         <v>45188</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28231,7 +28242,7 @@
         <v>46288</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28304,7 +28315,7 @@
         <v>46246</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28377,7 +28388,7 @@
         <v>45089</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28450,7 +28461,7 @@
         <v>45251</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28523,7 +28534,7 @@
         <v>44869</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28596,7 +28607,7 @@
         <v>45350</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28669,7 +28680,7 @@
         <v>46248</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28742,7 +28753,7 @@
         <v>46169</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28815,7 +28826,7 @@
         <v>44713</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28888,7 +28899,7 @@
         <v>45999</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28966,7 +28977,7 @@
         <v>45155</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29039,7 +29050,7 @@
         <v>45182</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29112,7 +29123,7 @@
         <v>45540</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29185,7 +29196,7 @@
         <v>45188</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29258,7 +29269,7 @@
         <v>44741</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29331,7 +29342,7 @@
         <v>45152</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29409,7 +29420,7 @@
         <v>45321</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29482,7 +29493,7 @@
         <v>45251</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29555,7 +29566,7 @@
         <v>44923</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29628,7 +29639,7 @@
         <v>44939</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29701,7 +29712,7 @@
         <v>46296</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29774,7 +29785,7 @@
         <v>45323</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29847,7 +29858,7 @@
         <v>44739</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29920,7 +29931,7 @@
         <v>45218</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29993,7 +30004,7 @@
         <v>46255</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30091,7 +30102,7 @@
         <v>46136</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30164,7 +30175,7 @@
         <v>45558</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30237,7 +30248,7 @@
         <v>44872</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30310,7 +30321,7 @@
         <v>45645</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30383,7 +30394,7 @@
         <v>45106</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30461,7 +30472,7 @@
         <v>44756</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30534,7 +30545,7 @@
         <v>45764</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30607,7 +30618,7 @@
         <v>45145</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30680,7 +30691,7 @@
         <v>44931</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30753,7 +30764,7 @@
         <v>45022</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30826,7 +30837,7 @@
         <v>44643</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30899,7 +30910,7 @@
         <v>45238</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30972,7 +30983,7 @@
         <v>45054</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31045,7 +31056,7 @@
         <v>45188</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31118,7 +31129,7 @@
         <v>45747</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31191,7 +31202,7 @@
         <v>44915</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31264,7 +31275,7 @@
         <v>45715</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31337,7 +31348,7 @@
         <v>45670</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31410,7 +31421,7 @@
         <v>45091</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31483,7 +31494,7 @@
         <v>45560</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31556,7 +31567,7 @@
         <v>45649</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31634,7 +31645,7 @@
         <v>45537</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31707,7 +31718,7 @@
         <v>45646</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31785,7 +31796,7 @@
         <v>44614</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31858,7 +31869,7 @@
         <v>45525</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31931,7 +31942,7 @@
         <v>44981</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32004,7 +32015,7 @@
         <v>45468</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32077,7 +32088,7 @@
         <v>44942</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32150,7 +32161,7 @@
         <v>44971</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32223,7 +32234,7 @@
         <v>44545</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32296,7 +32307,7 @@
         <v>44677</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32369,7 +32380,7 @@
         <v>44614</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32442,7 +32453,7 @@
         <v>44690</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32515,7 +32526,7 @@
         <v>44963</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32588,7 +32599,7 @@
         <v>45617</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32661,7 +32672,7 @@
         <v>45940</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32734,7 +32745,7 @@
         <v>46003</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32807,7 +32818,7 @@
         <v>46063</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32880,7 +32891,7 @@
         <v>46097</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>

--- a/Översikt MÖNSTERÅS.xlsx
+++ b/Översikt MÖNSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45470</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45525</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44622</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>46148</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45834</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>46196</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>44981</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45086</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45222</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>44537</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45679</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>46203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44665</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>46093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>44971</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44627</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45406</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45152</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45054</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>46008</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45160</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>45184</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>46113</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>46206</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44791</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>44621</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45250</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45539</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45674</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45106</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>45733</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>45282</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45999</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>46138</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>45364</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>45400</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>44873</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>44993</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44595</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>46283</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>45490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44827</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45350</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>45086</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>45534</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>45314</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>45456</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>45540</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44791</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>45455</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>45022</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>46275</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>44966</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>44967</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44875</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45534</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>44939</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>45757</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45558</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>45188</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>45833</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>45405</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45091</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>46155</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44645</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45453</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45688</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>44827</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>45086</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>45278</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>44854</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>45463</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45091</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>45086</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>44876</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45434</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>45538</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>44886</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>45174</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>44827</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>46076</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>46238</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>46206</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>45525</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44511</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44799</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44753</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44537</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44604</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44487</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>44824</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44651</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>44690</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44698</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44865</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>44865</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44546</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44874</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>44489</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>44644</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>44573</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44593</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>44518</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>44511</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>44537</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>44606</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>44642</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44649</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>44820</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>44517</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>44727</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>44874</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>44865</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44882</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>44621</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>44519</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>44791</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44813</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>44972</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>44865</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>44991</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>45575</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45106</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>44817</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>45034</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45596</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>45441</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>44981</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45329</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>45272</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>44727</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45359</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45631</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45686</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45251</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45238</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>45028</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>45538</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44950</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45250</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>44537</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44511</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>45538</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>45747</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>45645</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45399</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>44928</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>44974</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45540</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>45271</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45459</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45114</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45350</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45400</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45279</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45097</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>44756</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>45764</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45013</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>45558</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>44872</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>44979</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>45540</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>45540</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>45086</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>45903</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>45068</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>45904</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>44915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44915</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>44915</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>45091</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>45132</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45670</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45715</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>45321</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45091</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>45560</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45569</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>44874</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>44904</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45162</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44981</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45649</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45714</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45649</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45008</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45790</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45537</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45106</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45355</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45646</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45539</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45540</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>45092</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>45089</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45792</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45792</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45560</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>44869</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>45145</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45152</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45708</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>44915</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45218</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45404</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45323</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45037</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>44643</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45188</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>45701</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>44904</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45638</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>44923</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>44923</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>45805</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45805</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45169</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>44638</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44806</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45085</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45597</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44931</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45274</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45685</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44923</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45097</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45015</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45251</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45574</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>45139</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45209</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44621</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45155</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45961</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45840</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45161</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45182</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45188</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45553</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45611</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45274</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>44739</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44802</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45786</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45763</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45314</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44904</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45314</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45280</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45738</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45738</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>44806</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45330</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>44600</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45182</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45022</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>44817</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45188</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45160</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45713</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44803</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45015</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>45876</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44939</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>45274</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>45054</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>45537</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>46097</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>45075</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>45113</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>45218</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45274</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>44802</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>45988</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>45987</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>45764</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45987</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45987</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>45022</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>46113</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>44897</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>46122</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44879</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>46126</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44537</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>46134</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44741</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44869</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45540</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45015</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45764</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44817</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>44904</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45540</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>46136</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45991</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>44922</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>45364</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>44593</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>45686</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>44869</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>45769</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45477</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>45152</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>44922</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>45575</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>45568</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>46069</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44713</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28109,7 +28109,7 @@
         <v>44621</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>45538</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>46050</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>46043</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>44593</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45987</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45639</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>46043</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45238</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>46043</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44917</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>44931</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44820</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45057</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>46050</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45537</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45538</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>46078</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45950</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>46157</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45880</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>46092</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>46169</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>46190</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>46195</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>46195</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>46160</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>46196</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>46171</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>46197</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>46202</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>46205</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>46204</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>46126</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46274</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>46230</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>46238</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>46282</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>46244</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>46288</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45999</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>46248</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>46246</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>46169</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>46296</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>46255</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>46136</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>46262</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>44614</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44677</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>44614</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>44690</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45525</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44981</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>45468</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44942</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>44971</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>44545</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>44963</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45617</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45940</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>46003</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>46063</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>46097</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>

--- a/Översikt MÖNSTERÅS.xlsx
+++ b/Översikt MÖNSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45470</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45525</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44622</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>46148</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45834</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>46196</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>44981</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45086</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45222</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>44537</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45679</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>46203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44665</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>46093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>44971</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44627</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45406</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45152</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45054</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>46008</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45160</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>45184</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>46113</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>46206</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44791</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>44621</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45250</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45539</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45674</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45106</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>45733</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>45282</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45999</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>46138</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>45364</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>45400</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>44873</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>44993</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44595</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>46283</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>45490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44827</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45350</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>45086</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>45534</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>45314</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>45456</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>45540</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44791</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>45455</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>45022</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>46275</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>44966</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>44967</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>44875</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45534</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>44939</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>45757</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45558</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>45188</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>45833</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>45405</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45091</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>46155</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44645</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45453</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45688</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>44827</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>45086</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>45278</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>44854</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>45463</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45091</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>45086</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>44876</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45434</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>45538</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>44886</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>45174</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>44827</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>46076</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>46238</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>46206</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>45525</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44511</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44799</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44753</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44537</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44604</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44487</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>44824</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44651</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>44690</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44698</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44865</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>44865</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44546</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44874</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>44489</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>44644</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>44573</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44593</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>44518</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>44511</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>44537</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>44606</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>44642</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44649</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>44820</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>44517</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>44727</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>44874</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>44865</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44882</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>44621</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>44519</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>44791</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44813</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>44972</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>44865</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>44991</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>45575</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>45106</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>44817</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>45034</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45596</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>45441</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>44981</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45329</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>45272</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>44727</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45359</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45631</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45686</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45251</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45238</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>45028</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>45538</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44950</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45250</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>44537</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44511</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>45538</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>45747</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>45645</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45399</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>44928</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>44974</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45540</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>45271</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45459</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45114</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45350</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45400</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45279</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45097</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>44756</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>45764</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16948,7 +16948,7 @@
         <v>45013</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>45558</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>44872</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>44979</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17240,7 +17240,7 @@
         <v>45540</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>45540</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>45086</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17459,7 +17459,7 @@
         <v>45903</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>45068</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>45904</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>44915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>44915</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>44915</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>45091</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>45132</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45670</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45715</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>45321</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>45091</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>45560</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45569</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>44874</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>44904</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45162</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44981</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45649</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45714</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45649</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45008</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>45790</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45537</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45106</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45355</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45646</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45539</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45540</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>45092</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>45089</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45792</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45792</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45560</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>44869</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>45145</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45152</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45708</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>44915</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45218</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45404</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45323</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45037</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>44643</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45188</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>45701</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>44904</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45638</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>44923</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>44923</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>45805</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45805</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45169</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>44638</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44806</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45085</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45597</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44931</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45274</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45685</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44923</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45097</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45015</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45251</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45574</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>45139</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45209</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44621</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45155</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45961</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45840</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45161</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45182</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45188</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45553</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45611</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45274</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>44739</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44802</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45786</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45763</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45314</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44904</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45314</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45280</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45738</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45738</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>44806</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45330</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>44600</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>45182</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45022</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>44817</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45188</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45160</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45713</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44803</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45015</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>45876</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44939</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>45274</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>45054</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>45537</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>46097</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>45075</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>45113</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>45218</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45274</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>44802</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>45988</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>45987</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>45764</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45987</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45987</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>45022</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>46113</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>44897</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>46122</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>44879</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>46126</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>44537</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>46134</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44741</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44869</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45540</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45015</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45764</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44817</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>44904</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45540</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>46136</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45991</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>44922</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>45364</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>44593</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>45686</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>44869</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>45769</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45477</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>45152</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27739,7 +27739,7 @@
         <v>44922</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>45575</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>45568</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>46069</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28036,7 +28036,7 @@
         <v>44713</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28109,7 +28109,7 @@
         <v>44621</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>45538</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>46050</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>46043</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>44593</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45987</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45639</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>46043</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45238</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>46043</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>44917</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>44931</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>44820</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45057</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>46050</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45537</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45538</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>46078</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45950</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>46157</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45880</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>46092</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>46169</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>46190</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>46195</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>46195</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>46160</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>46196</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>46171</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>46197</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30304,7 +30304,7 @@
         <v>46202</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>46205</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30450,7 +30450,7 @@
         <v>46204</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>46126</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>46274</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30669,7 +30669,7 @@
         <v>46230</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>46238</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30815,7 +30815,7 @@
         <v>46282</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>46244</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>46288</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45999</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>46248</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>46246</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>46169</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>46296</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>46255</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>46136</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>46262</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>44614</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>44677</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>44614</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>44690</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45525</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44981</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>45468</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44942</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>44971</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>44545</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>44963</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45617</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45940</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>46003</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>46063</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>46097</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>

--- a/Översikt MÖNSTERÅS.xlsx
+++ b/Översikt MÖNSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45470</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45525</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44622</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>46148</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45834</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>46196</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>44981</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45086</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45222</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>44537</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45679</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>46203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44665</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>46093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>44971</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44627</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45406</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45152</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>46008</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45160</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>45184</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>46113</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>46206</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44791</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>44621</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45539</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45282</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45733</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>45106</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45674</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>45250</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45999</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>46138</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>45364</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44873</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44595</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>46283</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>44993</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>45400</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>45490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44827</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45455</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>45540</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44791</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>45534</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>45086</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45350</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45314</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>46275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45456</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>45022</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>44966</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>44967</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45188</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45091</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>46155</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>45405</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>44939</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>44875</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>45558</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>45534</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45757</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>45833</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>45453</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44645</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45688</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>44854</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44827</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>44876</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>45463</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>45086</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>45278</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>45538</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45086</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>46076</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45174</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44827</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>46238</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45091</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45434</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>46206</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>44886</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>45525</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44511</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44799</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44753</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44537</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44604</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44487</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>44824</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44651</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>44690</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44698</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44865</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>44865</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44546</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44489</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>44606</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>44537</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>44649</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>44517</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44727</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>44882</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44518</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>44519</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>44573</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>44511</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>44820</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>44865</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>44874</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>44621</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>44874</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44644</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44593</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44642</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>44791</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>45250</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>45359</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>44537</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>44727</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>45114</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>45161</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>45459</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>45057</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45132</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>44879</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>44621</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45106</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>44802</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45028</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45553</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>45569</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45540</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45540</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45539</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>45540</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>45355</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44923</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44803</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>44874</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>44981</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45209</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>45568</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>45441</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>44511</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44922</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>44928</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>44806</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45477</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45162</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45008</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>44817</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44974</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45015</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45097</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45274</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44813</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45364</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45097</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>44817</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>44638</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45274</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45540</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>44621</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45764</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45538</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44917</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45769</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45091</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44865</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>46136</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>46069</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>44593</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>46050</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45686</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45538</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45152</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>46043</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45903</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45904</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45638</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>44972</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>44991</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45279</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44904</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>44904</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45238</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>46157</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45068</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45961</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45880</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45596</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>45950</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45329</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45330</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45631</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45399</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>44600</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>45274</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>44904</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45314</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45987</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45987</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45987</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45037</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>45713</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45988</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45597</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>44981</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45272</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>46169</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45034</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45314</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45092</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45537</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45182</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45538</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45404</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45015</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>44820</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>44806</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45639</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>46043</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45987</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>46043</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45113</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>45013</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45764</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>44897</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44979</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>46050</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45085</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>44802</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45537</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45538</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45271</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45015</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45086</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44931</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45738</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45738</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>46078</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45169</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45611</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45274</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>46190</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45022</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>46092</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>46160</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>46195</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>46171</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>44915</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>46195</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>45686</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>44915</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>44915</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>46097</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45139</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>46197</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>44817</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44923</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>46196</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>46113</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44869</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>45575</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>46122</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>45685</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>44537</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>45218</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>46126</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>45574</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>46202</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>45560</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>45160</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>46204</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>46134</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45540</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45991</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>44593</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>46205</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>44869</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>45400</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44922</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44904</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>46126</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>45280</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45075</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44950</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45575</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45188</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45089</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45251</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>44869</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45350</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>46230</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44713</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45155</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45182</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>46274</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45540</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45188</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44741</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45152</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45321</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>46238</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45251</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>44923</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>44939</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45323</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>44739</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45218</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>46282</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>46244</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45558</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>44872</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45645</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>46288</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>46246</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45106</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>46248</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>46169</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45999</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44756</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45764</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45145</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>44931</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>45022</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44643</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45238</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45054</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45188</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45747</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>46296</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>44915</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>46255</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>46136</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>45715</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45670</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45091</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>45560</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>45649</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45537</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>45646</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45714</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>45649</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>45790</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>45708</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>45792</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>45792</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>46262</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45701</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>45805</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>45805</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>45840</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45763</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>45786</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45876</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>44614</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>45525</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>44981</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45468</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>44942</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44971</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>44545</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44677</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>44614</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>44690</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>44963</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45617</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45940</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>46003</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>46063</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>46097</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>

--- a/Översikt MÖNSTERÅS.xlsx
+++ b/Översikt MÖNSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45470</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45525</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44622</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>46148</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45834</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>46196</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>44981</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45086</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45222</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>44537</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45679</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45846</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>46203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44665</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>46093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>44971</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44627</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45406</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45152</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>46008</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45160</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>45184</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>46113</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>46206</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44791</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>44621</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45539</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45282</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45733</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>45106</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45674</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>45250</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45999</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>46138</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>45364</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>45840</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>44873</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44595</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>46283</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>44993</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>45400</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>45490</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44827</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45455</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>45540</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44791</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>45534</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>45086</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45350</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45314</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>46275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45456</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>45022</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>44966</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>44967</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>45525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45188</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45091</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>46155</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>45405</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>44939</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>44875</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>45558</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>45534</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45757</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>45833</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>45453</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44645</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45688</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>44854</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44827</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>44876</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>45463</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>45086</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>45278</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>45538</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>45086</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>46076</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45174</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44827</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>46238</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45091</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>45434</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>46206</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>44886</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>45525</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44511</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44799</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>44753</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44537</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44604</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44487</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>44824</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44651</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>44690</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44698</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44865</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>44865</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44546</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44489</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>44606</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>44537</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>44649</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>44517</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>44727</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>44882</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44518</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>44519</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>44573</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>44511</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>44820</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>44865</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>44874</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>44621</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>44874</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44644</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44593</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44642</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13862,7 +13862,7 @@
         <v>44791</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>45250</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>45359</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>44537</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>44727</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>45114</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>45161</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>45459</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>45057</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45132</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>44879</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>44621</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45106</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>44802</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>45028</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45553</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>45569</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45540</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45540</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45539</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>45540</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>45355</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>44923</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44803</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>44874</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>44981</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45209</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>45568</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>45441</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>44511</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44922</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>44928</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>44806</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45477</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45162</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45008</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>44817</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44974</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45015</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45097</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45274</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44813</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45364</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45097</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>44817</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>44638</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45274</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45540</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>44621</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45764</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45538</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44917</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45769</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45091</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44865</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>46136</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>46069</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>44593</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>46050</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45686</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45538</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45152</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>46043</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45903</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45904</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45638</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>44972</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>44991</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45279</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44904</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>44904</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45238</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>46157</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45068</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45961</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45880</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45596</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>45950</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45329</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45330</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45631</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45399</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>44600</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>45274</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>44904</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45314</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45987</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45987</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45987</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45037</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>45713</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45988</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45597</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>44981</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45272</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>46169</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45034</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45314</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45092</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45537</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45182</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45538</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45404</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45015</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>44820</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>44806</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45639</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>46043</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45987</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>46043</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45113</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>45013</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45764</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>44897</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44979</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>46050</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45085</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>44802</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45537</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45538</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45271</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45015</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45086</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44931</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45738</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45738</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>46078</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45169</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>45611</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45274</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>46190</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45022</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>46092</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>46160</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>46195</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>46171</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>44915</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>46195</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>45686</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>44915</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>44915</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>46097</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45139</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>46197</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>44817</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44923</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>46196</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>46113</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44869</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>45575</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>46122</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>45685</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>44537</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>45218</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>46126</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>45574</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>46202</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>45560</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>45160</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>46204</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>46134</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45540</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45991</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>44593</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>46205</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>44869</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>45400</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44922</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44904</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>46126</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>45280</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45075</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44950</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45575</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45188</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45089</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45251</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>44869</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45350</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>46230</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>44713</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45155</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45182</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>46274</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45540</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45188</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>44741</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45152</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45321</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>46238</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45251</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>44923</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>44939</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45323</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>44739</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45218</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>46282</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>46244</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45558</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>44872</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45645</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>46288</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>46246</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45106</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>46248</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>46169</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28980,7 +28980,7 @@
         <v>45999</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>44756</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45764</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45145</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>44931</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>45022</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44643</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45238</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45054</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45188</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45747</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>46296</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>44915</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>46255</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>46136</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30105,7 +30105,7 @@
         <v>45715</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45670</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45091</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>45560</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>45649</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>45537</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>45646</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45714</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>45649</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>45790</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>45708</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>45792</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>45792</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>46262</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45701</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>45805</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>45805</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>45840</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45763</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>45786</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45876</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>44614</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>45525</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>44981</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45468</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>44942</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44971</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>44545</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44677</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>44614</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>44690</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>44963</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45617</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45940</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>46003</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>46063</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>46097</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>

--- a/Översikt MÖNSTERÅS.xlsx
+++ b/Översikt MÖNSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45470</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45525</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44622</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>46148</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45834</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>46196</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>44981</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45086</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45222</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>44537</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45679</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>46203</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>45846</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44665</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>46093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>44971</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44627</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45406</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45152</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45054</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>46008</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>46206</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>46113</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45160</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>45184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44791</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>44621</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45733</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45282</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>46138</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>45250</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45539</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>45674</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45106</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>45840</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>45364</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>45400</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>46283</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44873</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>44993</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>44595</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>45490</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>44827</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>45086</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>45534</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>45456</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>46314</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>46275</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>44791</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>45455</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>45350</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>45314</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>45540</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>45022</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44966</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44967</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>45525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>45091</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>45534</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45757</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>45833</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44875</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>44939</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>45558</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>46155</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>45188</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45405</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44645</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45453</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45688</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44827</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>44827</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>45086</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>45278</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45463</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>45086</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44854</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>46238</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>46076</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>44886</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>46206</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>44876</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>45174</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>45091</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>45434</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>45538</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>45525</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>44511</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>44799</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>44753</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44537</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>44604</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44824</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44651</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44690</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>44698</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         <v>44865</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>44865</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>44546</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>44606</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>44537</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>44649</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>44517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44727</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>44882</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>44518</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>44519</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>44573</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>44511</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>44874</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>44865</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44820</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>44621</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>44874</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>44644</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44593</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>44642</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>44791</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>44869</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>45015</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44991</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>44817</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>44904</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45251</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>45364</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>45903</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>45904</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45880</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45477</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>44922</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45575</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45568</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>44713</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>44813</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>45639</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>46169</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45238</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>44917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>44931</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>44820</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45057</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>44817</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45537</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45441</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>44865</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>45575</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45106</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>45034</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>45596</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44981</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45329</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>44727</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45359</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>45631</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45238</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>45028</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>45538</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>45961</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>46190</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>45399</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>46195</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>44928</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>46195</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>46160</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>46196</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>46171</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>46197</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>45540</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>46202</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>45350</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>46205</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44756</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>44974</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>46204</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45558</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>46126</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>45988</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>45987</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>45987</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>45987</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44872</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>45086</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45670</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45715</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45091</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>45560</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>46230</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>45649</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>45271</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45714</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45649</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>46238</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45459</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45790</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45537</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45646</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>46282</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>46244</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45792</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45792</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45708</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>46288</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>46043</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45987</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>46043</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45701</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46050</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45999</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>46248</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45805</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>45805</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>45279</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>46246</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>46169</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>46296</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>46078</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>46255</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45013</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>46136</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45840</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>46092</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>46097</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45786</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45763</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>44979</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>46113</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45540</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45540</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>46122</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45068</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>46126</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45876</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>46134</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>44915</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44915</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44915</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45091</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45540</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45321</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45569</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>44874</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45764</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>46262</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45540</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>44904</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>46136</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45991</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>44922</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44593</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>45686</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44869</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>45769</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45152</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>46069</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45008</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45092</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>44621</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45538</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>46314</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>46050</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>44593</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45560</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44869</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45145</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45152</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>46043</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44915</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45404</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45037</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45538</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>44904</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44923</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>44923</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44638</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>45085</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45597</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44931</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45274</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45950</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44923</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>46157</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45015</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45251</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45574</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45139</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>45161</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45553</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45611</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45274</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44739</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45738</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>45738</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>44806</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45182</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45022</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>44817</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>45188</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>45160</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45713</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>45054</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45764</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>44972</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45272</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45686</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>44950</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>45250</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44537</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>44511</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45538</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45747</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45645</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45114</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>45400</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45097</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45764</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45132</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45162</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44981</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45106</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>45355</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>45539</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>45540</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45089</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45218</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>45323</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>44643</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>45188</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>45638</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>45169</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>44806</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>45685</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45097</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>45209</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>44621</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45155</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45182</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45188</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29889,7 +29889,7 @@
         <v>44802</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>45314</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>44904</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45314</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>45280</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>45330</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>44600</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>44803</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>45015</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44939</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45274</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>45537</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45075</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45113</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>45218</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>45274</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44802</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>45022</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44897</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>44879</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44537</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44741</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>44614</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>44677</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44614</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44690</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>45525</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44981</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>45468</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44942</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>44971</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44545</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44963</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45617</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45940</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>46003</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>46063</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>46097</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>

--- a/Översikt MÖNSTERÅS.xlsx
+++ b/Översikt MÖNSTERÅS.xlsx
@@ -601,7 +601,7 @@
         <v>46008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>45470</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45525</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>45715</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44622</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>46148</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45434</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>45834</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>46196</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>44981</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45086</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45222</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>44537</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45679</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>46203</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>45846</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>44665</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>46093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>44971</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44627</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45406</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45152</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45054</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>46008</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>46206</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>46113</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>45160</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>45184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44791</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>44621</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45733</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45282</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>46138</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>45250</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45539</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>45674</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45106</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>45840</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>45364</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>45400</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>46283</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44873</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>44993</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>44595</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>45490</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>44827</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>45086</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>45534</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>45456</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>46314</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>46275</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>44791</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>45455</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>45350</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>45314</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>45540</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>45022</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         <v>44966</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44967</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>45525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>45091</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>45534</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45757</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>45833</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44875</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>44939</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>45558</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>46155</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>45188</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45405</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44645</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45453</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45688</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45792</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>44634</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44827</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>44827</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>45086</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>45278</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>45463</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>45086</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44854</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>46238</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>46076</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>44886</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>46206</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>44876</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>45174</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>45091</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>45434</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>45538</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>45525</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>44511</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>44799</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>44753</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44537</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>44604</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44824</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44651</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>44690</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>44698</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         <v>44865</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>44865</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>44546</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>44606</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>44537</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>44649</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>44517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44727</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>44882</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>44518</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>44519</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>44573</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>44511</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>44874</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>44865</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44820</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>44621</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>44874</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>44644</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44593</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>44642</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>44791</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>44869</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>45015</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44991</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>44817</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>44904</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45251</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>45364</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>45903</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>45904</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45880</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45477</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>44922</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45575</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45568</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>44713</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>44813</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>45639</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>46169</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45238</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>44917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>44931</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>44820</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45057</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>44817</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45537</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45441</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>44865</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>45575</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45106</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>45034</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>45596</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44981</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45329</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>44727</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>45359</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>45631</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45238</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>45028</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>45538</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>45961</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>46190</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>45399</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>46195</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>44928</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>46195</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>46160</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>46196</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>46171</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>46197</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>45540</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>46202</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>45350</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>46205</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44756</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>44974</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>46204</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45558</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>46126</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
         <v>45988</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>45987</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>45987</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>45987</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>44872</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>45086</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45670</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18562,7 +18562,7 @@
         <v>45715</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45091</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>45560</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>46230</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>45649</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>45271</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45714</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45649</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>46238</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45459</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45790</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45537</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45646</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>46282</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>46244</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45792</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45792</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45708</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>46288</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>46043</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45987</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>46043</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45701</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46050</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45999</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>46248</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45805</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>45805</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>45279</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>46246</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>46169</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>46296</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>46078</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>46255</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45013</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>46136</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45840</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>46092</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>46097</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45786</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45763</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>44979</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>46113</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45540</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45540</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>46122</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45068</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>46126</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45876</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>46134</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>44915</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44915</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44915</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45091</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45540</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45321</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45569</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>44874</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45764</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>46262</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45540</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>44904</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>46136</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45991</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>44922</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44593</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>45686</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44869</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>45769</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45152</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>46069</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45008</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45092</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>44621</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45538</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>46314</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>46050</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>44593</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45560</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44869</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45145</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45152</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>46043</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44915</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45404</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45037</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45538</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>44904</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44923</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>44923</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44638</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>45085</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45597</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44931</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>45274</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45950</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44923</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>46157</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45015</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45251</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45574</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45139</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>45161</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45553</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>45611</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45274</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44739</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45738</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>45738</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>44806</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>45182</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45022</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>44817</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>45188</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>45160</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45713</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>45054</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45764</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>44972</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45272</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45686</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>44950</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>45250</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44537</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>44511</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45538</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45747</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45645</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45114</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>45400</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45097</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45764</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45132</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>45162</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44981</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45106</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>45355</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>45539</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>45540</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>45089</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45218</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>45323</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>44643</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>45188</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>45638</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>45169</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>44806</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>45685</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45097</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>45209</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>44621</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45155</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45182</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45188</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29889,7 +29889,7 @@
         <v>44802</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>45314</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>44904</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45314</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>45280</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>45330</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>44600</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>44803</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>45015</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44939</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>45274</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>45537</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45075</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45113</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>45218</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>45274</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44802</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>45022</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>44897</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>44879</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44537</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44741</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>44614</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>44677</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44614</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44690</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>45525</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44981</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>45468</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44942</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>44971</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44545</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44963</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45617</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45940</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>46003</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32532,7 +32532,7 @@
         <v>46063</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>46097</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
